--- a/reviews/a-envoyer/otea-filmakers-2026-08-10.xlsx
+++ b/reviews/a-envoyer/otea-filmakers-2026-08-10.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +48,10 @@
     <font>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <color rgb="FF1155CC"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="5">
@@ -99,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -114,6 +118,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -724,12 +731,12 @@
           <t>IG + TikTok</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>⚠️ visuel à venir</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>voir le visuel</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>Le plan dont je suis le plus fier, j'ai failli ne jamais le tourner. Trop fatigué, trop tard, presque rembillé.
 La leçon : le meilleur plan est souvent juste après le moment où tu voulais abandonner.
@@ -737,8 +744,8 @@
 #behindthescenes #videaste #oteafilmakers</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr"/>
-      <c r="I2" s="8" t="inlineStr"/>
+      <c r="H2" s="10" t="inlineStr"/>
+      <c r="I2" s="9" t="inlineStr"/>
     </row>
     <row r="3" ht="126" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
@@ -766,20 +773,20 @@
           <t>IG + TikTok</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>⚠️ visuel à venir</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>voir le visuel</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>✈️ Pourquoi je voyage pour filmer, alors que la plus belle lumière est parfois en bas de chez moi ?
 Parce que le déplacement change le regard. Loin de mes repères, je vois à nouveau. Le voyage n'est pas le sujet — c'est ce qui rouvre les yeux.
 #voyage #regard #videaste #oteafilmakers</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr"/>
+      <c r="H3" s="10" t="inlineStr"/>
+      <c r="I3" s="9" t="inlineStr"/>
     </row>
     <row r="4" ht="141" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -807,12 +814,12 @@
           <t>IG + TikTok</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>⚠️ visuel à venir</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>voir le visuel</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>Ma routine avant de tourner : pas de café, pas de musique. Juste 5 minutes à regarder. Sans caméra.
 On filme mieux ce qu'on a d'abord vraiment vu.
@@ -820,8 +827,8 @@
 #routine #creativite #videaste #oteafilmakers</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr"/>
+      <c r="H4" s="10" t="inlineStr"/>
+      <c r="I4" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
@@ -841,6 +848,11 @@
       <formula1>"✅ OK pour publier,✏️ À corriger (voir commentaire),⛔ Ne pas publier"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -886,7 +898,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-08T14:41:52</t>
+          <t>2026-08-10T08:13:46</t>
         </is>
       </c>
     </row>
@@ -924,7 +936,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>353096913</v>
+        <v>359747646</v>
       </c>
       <c r="C6" t="n">
         <v>4728418</v>
@@ -950,7 +962,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>353096919</v>
+        <v>359747660</v>
       </c>
       <c r="C7" t="n">
         <v>4728418</v>
@@ -975,7 +987,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>353096930</v>
+        <v>359747741</v>
       </c>
       <c r="C8" t="n">
         <v>4728418</v>
